--- a/app/uploads/Prueba para subir excel.xlsx
+++ b/app/uploads/Prueba para subir excel.xlsx
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3">
         <v>1</v>

--- a/app/uploads/Prueba para subir excel.xlsx
+++ b/app/uploads/Prueba para subir excel.xlsx
@@ -240,9 +240,6 @@
     <t>especialidad</t>
   </si>
   <si>
-    <t>Pepito</t>
-  </si>
-  <si>
     <t>martinez</t>
   </si>
   <si>
@@ -271,6 +268,9 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>Pepe</t>
   </si>
 </sst>
 </file>
@@ -703,22 +703,22 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
         <v>73</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
       </c>
       <c r="D2">
         <v>400</v>
       </c>
       <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
         <v>76</v>
-      </c>
-      <c r="F2" t="s">
-        <v>77</v>
       </c>
       <c r="G2" t="s">
         <v>68</v>
@@ -747,25 +747,25 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
         <v>78</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
       </c>
       <c r="D3">
         <v>401</v>
       </c>
       <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
         <v>81</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>82</v>
-      </c>
-      <c r="G3" t="s">
-        <v>83</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>

--- a/app/uploads/Prueba para subir excel.xlsx
+++ b/app/uploads/Prueba para subir excel.xlsx
@@ -252,9 +252,6 @@
     <t>407A</t>
   </si>
   <si>
-    <t>Joaquín</t>
-  </si>
-  <si>
     <t>hernandez</t>
   </si>
   <si>
@@ -267,10 +264,13 @@
     <t>408B</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>Pepe</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Mary</t>
   </si>
 </sst>
 </file>
@@ -703,7 +703,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>73</v>
@@ -721,7 +721,7 @@
         <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -747,25 +747,25 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
       </c>
       <c r="D3">
         <v>401</v>
       </c>
       <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" t="s">
         <v>80</v>
       </c>
-      <c r="F3" t="s">
-        <v>81</v>
-      </c>
       <c r="G3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
